--- a/exports/trend_1d/LT_full_report.xlsx
+++ b/exports/trend_1d/LT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.93</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>1122.37</v>
+        <v>1048.3</v>
       </c>
       <c r="I2" t="n">
         <v>1081.34674488832</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>6.98</v>
+        <v>-0.08</v>
       </c>
       <c r="L2" t="n">
         <v>2.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0.39</v>
+        <v>1.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.51</v>
+        <v>6.6</v>
       </c>
       <c r="O2" t="n">
         <v>3.67</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>11.87</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42061</v>
+        <v>42062</v>
       </c>
       <c r="H3" t="n">
-        <v>1118.7</v>
+        <v>1172.63</v>
       </c>
       <c r="I3" t="n">
         <v>1153.272516954228</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.72</v>
+        <v>-11.86</v>
       </c>
       <c r="L3" t="n">
-        <v>10.32</v>
+        <v>12.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0.97</v>
+        <v>1.47</v>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>4.82</v>
       </c>
       <c r="O3" t="n">
         <v>-6.6</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42075</v>
+        <v>42076</v>
       </c>
       <c r="H4" t="n">
-        <v>1164.93</v>
+        <v>1128.1</v>
       </c>
       <c r="I4" t="n">
         <v>1131.671825576831</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.66</v>
+        <v>-3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>3.35</v>
+        <v>4.31</v>
       </c>
       <c r="M4" t="n">
         <v>0.48</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>11.6</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42104</v>
+        <v>42107</v>
       </c>
       <c r="H5" t="n">
-        <v>1176</v>
+        <v>1202.33</v>
       </c>
       <c r="I5" t="n">
         <v>1188.462929971465</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.25</v>
+        <v>-6.58</v>
       </c>
       <c r="L5" t="n">
-        <v>5.66</v>
+        <v>6.79</v>
       </c>
       <c r="M5" t="n">
         <v>1.3</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.45</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H6" t="n">
-        <v>1119.07</v>
+        <v>1111.8</v>
       </c>
       <c r="I6" t="n">
         <v>1113.539144085587</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.92</v>
+        <v>-7.53</v>
       </c>
       <c r="L6" t="n">
-        <v>7.46</v>
+        <v>8.1</v>
       </c>
       <c r="M6" t="n">
         <v>0.12</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>8.92</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42153</v>
+        <v>42156</v>
       </c>
       <c r="H7" t="n">
-        <v>1102.97</v>
+        <v>1137.03</v>
       </c>
       <c r="I7" t="n">
         <v>1134.40526931455</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K7" t="n">
-        <v>0.79</v>
+        <v>-2.27</v>
       </c>
       <c r="L7" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.06</v>
+        <v>3.09</v>
       </c>
       <c r="O7" t="n">
         <v>-0.65</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H8" t="n">
-        <v>1201.57</v>
+        <v>1162.23</v>
       </c>
       <c r="I8" t="n">
         <v>1184.320201664099</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K8" t="n">
-        <v>5.68</v>
+        <v>2.22</v>
       </c>
       <c r="L8" t="n">
         <v>3.67</v>
@@ -897,7 +992,7 @@
         <v>1.89</v>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>3.27</v>
       </c>
       <c r="O8" t="n">
         <v>3.09</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42292</v>
+        <v>42293</v>
       </c>
       <c r="H9" t="n">
-        <v>1040.33</v>
+        <v>1069.97</v>
       </c>
       <c r="I9" t="n">
         <v>1059.732526411149</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K9" t="n">
-        <v>10.49</v>
+        <v>7.94</v>
       </c>
       <c r="L9" t="n">
         <v>5.79</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42305</v>
+        <v>42306</v>
       </c>
       <c r="H10" t="n">
-        <v>995.17</v>
+        <v>980.5</v>
       </c>
       <c r="I10" t="n">
         <v>988.7069882619876</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.99</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>7.6</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>0.32</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.64</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H11" t="n">
-        <v>758.6</v>
+        <v>804.73</v>
       </c>
       <c r="I11" t="n">
         <v>789.2544250197648</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K11" t="n">
-        <v>22.63</v>
+        <v>17.93</v>
       </c>
       <c r="L11" t="n">
         <v>1.83</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>14.32</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="H12" t="n">
-        <v>1039.23</v>
+        <v>995.8</v>
       </c>
       <c r="I12" t="n">
         <v>1010.664989318256</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K12" t="n">
-        <v>29.14</v>
+        <v>23.74</v>
       </c>
       <c r="L12" t="n">
         <v>6.02</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.55</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42620</v>
+        <v>42621</v>
       </c>
       <c r="H13" t="n">
-        <v>1012.17</v>
+        <v>1026.33</v>
       </c>
       <c r="I13" t="n">
         <v>1021.496959301135</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.64</v>
+        <v>-3.07</v>
       </c>
       <c r="L13" t="n">
         <v>6.18</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.12</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42639</v>
+        <v>42640</v>
       </c>
       <c r="H14" t="n">
-        <v>977.13</v>
+        <v>957.6</v>
       </c>
       <c r="I14" t="n">
         <v>963.5362491763069</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.79</v>
+        <v>-6.7</v>
       </c>
       <c r="L14" t="n">
-        <v>5.42</v>
+        <v>7.02</v>
       </c>
       <c r="M14" t="n">
         <v>1.96</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.87</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H15" t="n">
-        <v>925</v>
+        <v>941.5700000000001</v>
       </c>
       <c r="I15" t="n">
         <v>931.4675473504076</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="L15" t="n">
         <v>5.82</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.09</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42965</v>
+        <v>42968</v>
       </c>
       <c r="H16" t="n">
-        <v>1130.6</v>
+        <v>1127.1</v>
       </c>
       <c r="I16" t="n">
         <v>1127.90406895008</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K16" t="n">
-        <v>20.08</v>
+        <v>19.7</v>
       </c>
       <c r="L16" t="n">
         <v>2.16</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.49</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42986</v>
+        <v>42989</v>
       </c>
       <c r="H17" t="n">
-        <v>1172.4</v>
+        <v>1217.85</v>
       </c>
       <c r="I17" t="n">
         <v>1174.44454030936</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.02</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>4.87</v>
+        <v>8.69</v>
       </c>
       <c r="M17" t="n">
         <v>0.88</v>
       </c>
       <c r="N17" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="O17" t="n">
         <v>-0.31</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>8.81</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H18" t="n">
-        <v>1184.8</v>
+        <v>1165.2</v>
       </c>
       <c r="I18" t="n">
         <v>1166.334703355426</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.71</v>
+        <v>-4.32</v>
       </c>
       <c r="L18" t="n">
-        <v>5.36</v>
+        <v>5.98</v>
       </c>
       <c r="M18" t="n">
         <v>0.67</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>7.6</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H19" t="n">
-        <v>1142.55</v>
+        <v>1204.2</v>
       </c>
       <c r="I19" t="n">
         <v>1197.010090878364</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K19" t="n">
-        <v>1.94</v>
+        <v>-3.35</v>
       </c>
       <c r="L19" t="n">
-        <v>1.87</v>
+        <v>4.27</v>
       </c>
       <c r="M19" t="n">
         <v>1.18</v>
       </c>
       <c r="N19" t="n">
-        <v>0.86</v>
+        <v>5.4</v>
       </c>
       <c r="O19" t="n">
         <v>-1.65</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.18</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="H20" t="n">
-        <v>1353.05</v>
+        <v>1333.75</v>
       </c>
       <c r="I20" t="n">
         <v>1335.438138535202</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K20" t="n">
-        <v>12.36</v>
+        <v>10.76</v>
       </c>
       <c r="L20" t="n">
         <v>4.49</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.61</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43203</v>
+        <v>43206</v>
       </c>
       <c r="H21" t="n">
-        <v>1354.85</v>
+        <v>1368.1</v>
       </c>
       <c r="I21" t="n">
         <v>1357.791081414245</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.58</v>
+        <v>-2.58</v>
       </c>
       <c r="L21" t="n">
         <v>2.91</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>6.31</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43237</v>
+        <v>43238</v>
       </c>
       <c r="H22" t="n">
-        <v>1355.95</v>
+        <v>1315.55</v>
       </c>
       <c r="I22" t="n">
         <v>1323.423796625225</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.89</v>
+        <v>-3.84</v>
       </c>
       <c r="L22" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="M22" t="n">
         <v>0.68</v>
       </c>
       <c r="N22" t="n">
-        <v>1.81</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
         <v>0.98</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.17</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H23" t="n">
-        <v>1279.15</v>
+        <v>1324</v>
       </c>
       <c r="I23" t="n">
         <v>1305.819875725045</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K23" t="n">
-        <v>2.77</v>
+        <v>-0.64</v>
       </c>
       <c r="L23" t="n">
         <v>8.32</v>
@@ -1752,7 +2027,7 @@
         <v>1.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.51</v>
       </c>
       <c r="O23" t="n">
         <v>-2.98</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43326</v>
+        <v>43328</v>
       </c>
       <c r="H24" t="n">
-        <v>1253.25</v>
+        <v>1231.65</v>
       </c>
       <c r="I24" t="n">
         <v>1237.865367684946</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.34</v>
+        <v>-6.98</v>
       </c>
       <c r="L24" t="n">
-        <v>5.58</v>
+        <v>7.4</v>
       </c>
       <c r="M24" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="N24" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="O24" t="n">
         <v>3.51</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.16</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43329</v>
+        <v>43332</v>
       </c>
       <c r="H25" t="n">
-        <v>1240.15</v>
+        <v>1323.7</v>
       </c>
       <c r="I25" t="n">
         <v>1312.48248256465</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-7.47</v>
       </c>
       <c r="L25" t="n">
-        <v>2.52</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6</v>
+        <v>4.83</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6899999999999999</v>
+        <v>6.74</v>
       </c>
       <c r="O25" t="n">
         <v>-1.72</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43370</v>
+        <v>43371</v>
       </c>
       <c r="H26" t="n">
-        <v>1309.9</v>
+        <v>1272.1</v>
       </c>
       <c r="I26" t="n">
         <v>1295.93821214602</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.04</v>
+        <v>-3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>5.56</v>
       </c>
       <c r="M26" t="n">
         <v>0.54</v>
       </c>
       <c r="N26" t="n">
-        <v>1.71</v>
+        <v>2.89</v>
       </c>
       <c r="O26" t="n">
         <v>6.74</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.25</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43403</v>
+        <v>43404</v>
       </c>
       <c r="H27" t="n">
-        <v>1271.25</v>
+        <v>1297.5</v>
       </c>
       <c r="I27" t="n">
         <v>1284.905468400738</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2</v>
       </c>
       <c r="L27" t="n">
         <v>3.51</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.44</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43476</v>
+        <v>43479</v>
       </c>
       <c r="H28" t="n">
-        <v>1369.6</v>
+        <v>1333.9</v>
       </c>
       <c r="I28" t="n">
         <v>1356.086403814626</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K28" t="n">
-        <v>5.56</v>
+        <v>2.81</v>
       </c>
       <c r="L28" t="n">
         <v>3.72</v>
@@ -2037,7 +2372,7 @@
         <v>1.8</v>
       </c>
       <c r="N28" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="O28" t="n">
         <v>2.06</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.48</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43529</v>
+        <v>43530</v>
       </c>
       <c r="H29" t="n">
-        <v>1305.8</v>
+        <v>1317</v>
       </c>
       <c r="I29" t="n">
         <v>1311.851886974082</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K29" t="n">
-        <v>2.11</v>
+        <v>1.27</v>
       </c>
       <c r="L29" t="n">
         <v>2.5</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.91</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H30" t="n">
-        <v>1355.5</v>
+        <v>1317.65</v>
       </c>
       <c r="I30" t="n">
         <v>1327.958062898219</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K30" t="n">
-        <v>2.92</v>
+        <v>0.05</v>
       </c>
       <c r="L30" t="n">
         <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="N30" t="n">
-        <v>2.25</v>
+        <v>2.79</v>
       </c>
       <c r="O30" t="n">
         <v>0.86</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>6.87</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H31" t="n">
-        <v>1361.9</v>
+        <v>1451.45</v>
       </c>
       <c r="I31" t="n">
         <v>1402.434825261777</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.36</v>
+        <v>-10.15</v>
       </c>
       <c r="L31" t="n">
-        <v>4.09</v>
+        <v>10.42</v>
       </c>
       <c r="M31" t="n">
-        <v>0.42</v>
+        <v>2.8</v>
       </c>
       <c r="N31" t="n">
-        <v>1.85</v>
+        <v>6.58</v>
       </c>
       <c r="O31" t="n">
         <v>-2.79</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H32" t="n">
-        <v>1558.35</v>
+        <v>1490.35</v>
       </c>
       <c r="I32" t="n">
         <v>1492.833256053543</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K32" t="n">
-        <v>7.37</v>
+        <v>2.68</v>
       </c>
       <c r="L32" t="n">
         <v>3.54</v>
       </c>
       <c r="M32" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="N32" t="n">
-        <v>3.43</v>
+        <v>4.36</v>
       </c>
       <c r="O32" t="n">
         <v>6.58</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>8.57</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H33" t="n">
-        <v>1300.7</v>
+        <v>1411.5</v>
       </c>
       <c r="I33" t="n">
         <v>1389.062458371257</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K33" t="n">
-        <v>12.73</v>
+        <v>5.29</v>
       </c>
       <c r="L33" t="n">
         <v>4.09</v>
@@ -2322,7 +2717,7 @@
         <v>1.83</v>
       </c>
       <c r="N33" t="n">
-        <v>3.66</v>
+        <v>8.52</v>
       </c>
       <c r="O33" t="n">
         <v>-4.36</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>12.42</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43782</v>
+        <v>43783</v>
       </c>
       <c r="H34" t="n">
-        <v>1393</v>
+        <v>1380.45</v>
       </c>
       <c r="I34" t="n">
         <v>1385.383018388593</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.31</v>
+        <v>-2.2</v>
       </c>
       <c r="L34" t="n">
         <v>8.67</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.08</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43853</v>
+        <v>43854</v>
       </c>
       <c r="H35" t="n">
-        <v>1332.3</v>
+        <v>1359.2</v>
       </c>
       <c r="I35" t="n">
         <v>1353.979921396842</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K35" t="n">
-        <v>3.49</v>
+        <v>1.54</v>
       </c>
       <c r="L35" t="n">
         <v>2.71</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H36" t="n">
-        <v>1369.3</v>
+        <v>1287.4</v>
       </c>
       <c r="I36" t="n">
         <v>1299.187163666921</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>0.74</v>
+        <v>-5.28</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>5.83</v>
       </c>
       <c r="M36" t="n">
         <v>1.41</v>
       </c>
       <c r="N36" t="n">
-        <v>0.78</v>
+        <v>5.98</v>
       </c>
       <c r="O36" t="n">
         <v>2.02</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.73</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43937</v>
+        <v>43938</v>
       </c>
       <c r="H37" t="n">
-        <v>911.65</v>
+        <v>932.9</v>
       </c>
       <c r="I37" t="n">
         <v>930.0925439982539</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K37" t="n">
-        <v>29.19</v>
+        <v>27.54</v>
       </c>
       <c r="L37" t="n">
         <v>7.48</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>17.72</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44077</v>
+        <v>44078</v>
       </c>
       <c r="H38" t="n">
-        <v>961.15</v>
+        <v>942.5</v>
       </c>
       <c r="I38" t="n">
         <v>942.636620793136</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K38" t="n">
-        <v>3.03</v>
+        <v>1.03</v>
       </c>
       <c r="L38" t="n">
         <v>15.14</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>7.99</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44123</v>
+        <v>44124</v>
       </c>
       <c r="H39" t="n">
-        <v>902.9</v>
+        <v>917.3</v>
       </c>
       <c r="I39" t="n">
         <v>916.3383553475797</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K39" t="n">
-        <v>4.2</v>
+        <v>2.67</v>
       </c>
       <c r="L39" t="n">
         <v>1.45</v>
       </c>
       <c r="M39" t="n">
-        <v>1.13</v>
+        <v>1.78</v>
       </c>
       <c r="N39" t="n">
         <v>4.53</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.1</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H40" t="n">
-        <v>1437.65</v>
+        <v>1428.1</v>
       </c>
       <c r="I40" t="n">
         <v>1428.708914134516</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K40" t="n">
-        <v>56.73</v>
+        <v>55.69</v>
       </c>
       <c r="L40" t="n">
         <v>0.9399999999999999</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.16</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="H41" t="n">
-        <v>1418.05</v>
+        <v>1443.25</v>
       </c>
       <c r="I41" t="n">
         <v>1432.628810321654</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7</v>
+        <v>-1.06</v>
       </c>
       <c r="L41" t="n">
         <v>2.91</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>8.18</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44365</v>
+        <v>44368</v>
       </c>
       <c r="H42" t="n">
-        <v>1476</v>
+        <v>1467.05</v>
       </c>
       <c r="I42" t="n">
         <v>1468.08772761987</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K42" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="L42" t="n">
         <v>2.3</v>
       </c>
       <c r="M42" t="n">
-        <v>0.66</v>
+        <v>1.08</v>
       </c>
       <c r="N42" t="n">
         <v>1.93</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>5.45</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44391</v>
+        <v>44392</v>
       </c>
       <c r="H43" t="n">
-        <v>1544.7</v>
+        <v>1609.35</v>
       </c>
       <c r="I43" t="n">
         <v>1547.047948900436</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.29</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>5.65</v>
+        <v>10.77</v>
       </c>
       <c r="M43" t="n">
         <v>0.95</v>
       </c>
       <c r="N43" t="n">
-        <v>2.19</v>
+        <v>4.19</v>
       </c>
       <c r="O43" t="n">
         <v>-0.61</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H44" t="n">
-        <v>1849.9</v>
+        <v>1778.15</v>
       </c>
       <c r="I44" t="n">
         <v>1829.975009025457</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K44" t="n">
-        <v>14.95</v>
+        <v>10.49</v>
       </c>
       <c r="L44" t="n">
         <v>3.69</v>
       </c>
       <c r="M44" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="N44" t="n">
-        <v>2.86</v>
+        <v>3.88</v>
       </c>
       <c r="O44" t="n">
         <v>4.19</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.94</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H45" t="n">
-        <v>1895.9</v>
+        <v>1922.85</v>
       </c>
       <c r="I45" t="n">
         <v>1913.898098158152</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.62</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>7.36</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>1.08</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>6.23</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H46" t="n">
-        <v>1956.05</v>
+        <v>1899.9</v>
       </c>
       <c r="I46" t="n">
         <v>1945.439138162174</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>1.73</v>
+        <v>-1.19</v>
       </c>
       <c r="L46" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="M46" t="n">
         <v>1.07</v>
       </c>
       <c r="N46" t="n">
-        <v>2.37</v>
+        <v>2.87</v>
       </c>
       <c r="O46" t="n">
         <v>1.42</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.44</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H47" t="n">
-        <v>1790.1</v>
+        <v>1826.35</v>
       </c>
       <c r="I47" t="n">
         <v>1810.70687337501</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K47" t="n">
-        <v>5.78</v>
+        <v>3.87</v>
       </c>
       <c r="L47" t="n">
         <v>5.69</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7.95</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H48" t="n">
-        <v>1738.35</v>
+        <v>1705.75</v>
       </c>
       <c r="I48" t="n">
         <v>1729.907307098208</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.82</v>
+        <v>-6.6</v>
       </c>
       <c r="L48" t="n">
-        <v>6.1</v>
+        <v>7.63</v>
       </c>
       <c r="M48" t="n">
         <v>0.82</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H49" t="n">
-        <v>1556.15</v>
+        <v>1611.1</v>
       </c>
       <c r="I49" t="n">
         <v>1605.143866297002</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K49" t="n">
-        <v>8.77</v>
+        <v>5.55</v>
       </c>
       <c r="L49" t="n">
         <v>3.22</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.67</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H50" t="n">
-        <v>1888.2</v>
+        <v>1856.85</v>
       </c>
       <c r="I50" t="n">
         <v>1868.711333921444</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K50" t="n">
-        <v>17.2</v>
+        <v>15.25</v>
       </c>
       <c r="L50" t="n">
         <v>2.82</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>7.18</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44859</v>
+        <v>44861</v>
       </c>
       <c r="H51" t="n">
-        <v>1949.1</v>
+        <v>1964.05</v>
       </c>
       <c r="I51" t="n">
         <v>1950.287295149415</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.97</v>
+        <v>-5.77</v>
       </c>
       <c r="L51" t="n">
-        <v>5.27</v>
+        <v>6.19</v>
       </c>
       <c r="M51" t="n">
         <v>1.56</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H52" t="n">
-        <v>2109.95</v>
+        <v>2062.75</v>
       </c>
       <c r="I52" t="n">
         <v>2079.485041593945</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K52" t="n">
-        <v>7.43</v>
+        <v>5.03</v>
       </c>
       <c r="L52" t="n">
         <v>0.72</v>
@@ -3405,7 +4028,7 @@
         <v>0.76</v>
       </c>
       <c r="N52" t="n">
-        <v>1.69</v>
+        <v>2.24</v>
       </c>
       <c r="O52" t="n">
         <v>0.77</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.75</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44942</v>
+        <v>44943</v>
       </c>
       <c r="H53" t="n">
-        <v>2137.2</v>
+        <v>2213.1</v>
       </c>
       <c r="I53" t="n">
         <v>2195.38239123634</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.61</v>
+        <v>-7.29</v>
       </c>
       <c r="L53" t="n">
-        <v>4.95</v>
+        <v>7.52</v>
       </c>
       <c r="M53" t="n">
         <v>1.03</v>
       </c>
       <c r="N53" t="n">
-        <v>1.68</v>
+        <v>3.55</v>
       </c>
       <c r="O53" t="n">
         <v>-2.24</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.54</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44953</v>
+        <v>44956</v>
       </c>
       <c r="H54" t="n">
-        <v>2159.85</v>
+        <v>2112.9</v>
       </c>
       <c r="I54" t="n">
         <v>2125.100965588709</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.41</v>
+        <v>-4.53</v>
       </c>
       <c r="L54" t="n">
-        <v>3.89</v>
+        <v>5.84</v>
       </c>
       <c r="M54" t="n">
-        <v>0.29</v>
+        <v>1.41</v>
       </c>
       <c r="N54" t="n">
-        <v>1.49</v>
+        <v>2.17</v>
       </c>
       <c r="O54" t="n">
         <v>3.55</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H55" t="n">
-        <v>2257.75</v>
+        <v>2274.25</v>
       </c>
       <c r="I55" t="n">
         <v>2260.839061326731</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.86</v>
+        <v>-7.64</v>
       </c>
       <c r="L55" t="n">
-        <v>7.08</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>1.49</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.46</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45056</v>
+        <v>45057</v>
       </c>
       <c r="H56" t="n">
-        <v>2364.45</v>
+        <v>2242.15</v>
       </c>
       <c r="I56" t="n">
         <v>2255.918971764647</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>3.97</v>
+        <v>-1.41</v>
       </c>
       <c r="L56" t="n">
         <v>3.86</v>
       </c>
       <c r="M56" t="n">
-        <v>0.38</v>
+        <v>2.73</v>
       </c>
       <c r="N56" t="n">
-        <v>1.98</v>
+        <v>5.17</v>
       </c>
       <c r="O56" t="n">
         <v>0.73</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45083</v>
+        <v>45084</v>
       </c>
       <c r="H57" t="n">
-        <v>2277.95</v>
+        <v>2315.5</v>
       </c>
       <c r="I57" t="n">
         <v>2314.86682474172</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.6</v>
+        <v>-3.27</v>
       </c>
       <c r="L57" t="n">
-        <v>3.21</v>
+        <v>3.38</v>
       </c>
       <c r="M57" t="n">
         <v>0.6</v>
       </c>
       <c r="N57" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="O57" t="n">
         <v>-5.17</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.07</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H58" t="n">
-        <v>2958.3</v>
+        <v>2916.1</v>
       </c>
       <c r="I58" t="n">
         <v>2946.584372394403</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K58" t="n">
-        <v>27.76</v>
+        <v>25.94</v>
       </c>
       <c r="L58" t="n">
         <v>1.62</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>5</v>
+      </c>
+      <c r="U58" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>6.31</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45240</v>
+        <v>45242</v>
       </c>
       <c r="H59" t="n">
-        <v>3033.25</v>
+        <v>3052</v>
       </c>
       <c r="I59" t="n">
         <v>3047.340576979531</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.02</v>
+        <v>-4.66</v>
       </c>
       <c r="L59" t="n">
-        <v>4.39</v>
+        <v>4.93</v>
       </c>
       <c r="M59" t="n">
         <v>1.37</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>4.74</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H60" t="n">
-        <v>3479.75</v>
+        <v>3398</v>
       </c>
       <c r="I60" t="n">
         <v>3449.4551464379</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K60" t="n">
-        <v>14.02</v>
+        <v>11.34</v>
       </c>
       <c r="L60" t="n">
         <v>0.6899999999999999</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.92</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="H61" t="n">
-        <v>3477.55</v>
+        <v>3633.5</v>
       </c>
       <c r="I61" t="n">
         <v>3541.563334500062</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.34</v>
+        <v>-6.93</v>
       </c>
       <c r="L61" t="n">
-        <v>3.38</v>
+        <v>7.66</v>
       </c>
       <c r="M61" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>2.62</v>
+        <v>4.48</v>
       </c>
       <c r="O61" t="n">
         <v>-2.35</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45397</v>
+        <v>45398</v>
       </c>
       <c r="H62" t="n">
-        <v>3600.8</v>
+        <v>3543.45</v>
       </c>
       <c r="I62" t="n">
         <v>3574.835418051395</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.9</v>
+        <v>-2.48</v>
       </c>
       <c r="L62" t="n">
         <v>4.2</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.36</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45434</v>
+        <v>45435</v>
       </c>
       <c r="H63" t="n">
-        <v>3460.85</v>
+        <v>3585.4</v>
       </c>
       <c r="I63" t="n">
         <v>3547.891510162415</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K63" t="n">
-        <v>2.33</v>
+        <v>-1.18</v>
       </c>
       <c r="L63" t="n">
         <v>3.46</v>
@@ -4032,7 +4787,7 @@
         <v>1.43</v>
       </c>
       <c r="N63" t="n">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="O63" t="n">
         <v>-1.59</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>8.26</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H64" t="n">
-        <v>3897.15</v>
+        <v>3403.2</v>
       </c>
       <c r="I64" t="n">
         <v>3584.325263852701</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K64" t="n">
-        <v>8.69</v>
+        <v>-5.08</v>
       </c>
       <c r="L64" t="n">
-        <v>3.64</v>
+        <v>7.4</v>
       </c>
       <c r="M64" t="n">
         <v>1.29</v>
       </c>
       <c r="N64" t="n">
-        <v>0.64</v>
+        <v>12.67</v>
       </c>
       <c r="O64" t="n">
         <v>3.6</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>18.45</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45499</v>
+        <v>45502</v>
       </c>
       <c r="H65" t="n">
-        <v>3679.9</v>
+        <v>3774.95</v>
       </c>
       <c r="I65" t="n">
         <v>3756.755482596107</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.130000000000001</v>
+        <v>-10.92</v>
       </c>
       <c r="L65" t="n">
         <v>14.54</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>8.15</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H66" t="n">
-        <v>3665.7</v>
+        <v>3528</v>
       </c>
       <c r="I66" t="n">
         <v>3553.42295421023</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.89</v>
+        <v>-6.54</v>
       </c>
       <c r="L66" t="n">
-        <v>3.12</v>
+        <v>6.98</v>
       </c>
       <c r="M66" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="N66" t="n">
-        <v>3.01</v>
+        <v>3.76</v>
       </c>
       <c r="O66" t="n">
         <v>2.58</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45554</v>
+        <v>45555</v>
       </c>
       <c r="H67" t="n">
-        <v>3683.7</v>
+        <v>3793.9</v>
       </c>
       <c r="I67" t="n">
         <v>3748.433054068014</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.41</v>
+        <v>-7.54</v>
       </c>
       <c r="L67" t="n">
-        <v>6.52</v>
+        <v>7.99</v>
       </c>
       <c r="M67" t="n">
         <v>1.5</v>
       </c>
       <c r="N67" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="O67" t="n">
         <v>-3.76</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>6.86</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H68" t="n">
-        <v>3653.5</v>
+        <v>3497.65</v>
       </c>
       <c r="I68" t="n">
         <v>3593.808562721068</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.7</v>
+        <v>-7.81</v>
       </c>
       <c r="L68" t="n">
-        <v>4.07</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M68" t="n">
-        <v>0.64</v>
+        <v>1.94</v>
       </c>
       <c r="N68" t="n">
-        <v>1.5</v>
+        <v>4.27</v>
       </c>
       <c r="O68" t="n">
         <v>2.99</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45595</v>
+        <v>45596</v>
       </c>
       <c r="H69" t="n">
-        <v>3408.35</v>
+        <v>3622.3</v>
       </c>
       <c r="I69" t="n">
         <v>3557.323241095327</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K69" t="n">
-        <v>2.55</v>
+        <v>-3.56</v>
       </c>
       <c r="L69" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8</v>
+        <v>3.57</v>
       </c>
       <c r="N69" t="n">
-        <v>2.08</v>
+        <v>6.28</v>
       </c>
       <c r="O69" t="n">
         <v>-4.27</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.08</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H70" t="n">
-        <v>3716.35</v>
+        <v>3629.85</v>
       </c>
       <c r="I70" t="n">
         <v>3682.908534653124</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K70" t="n">
-        <v>2.6</v>
+        <v>0.21</v>
       </c>
       <c r="L70" t="n">
         <v>4.69</v>
@@ -4431,7 +5270,7 @@
         <v>1.49</v>
       </c>
       <c r="N70" t="n">
-        <v>1.82</v>
+        <v>2.33</v>
       </c>
       <c r="O70" t="n">
         <v>6.28</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>7.91</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H71" t="n">
-        <v>3351.05</v>
+        <v>3415.95</v>
       </c>
       <c r="I71" t="n">
         <v>3376.885964625587</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K71" t="n">
-        <v>7.68</v>
+        <v>5.89</v>
       </c>
       <c r="L71" t="n">
         <v>2.62</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>7.25</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H72" t="n">
-        <v>3420.15</v>
+        <v>3260.15</v>
       </c>
       <c r="I72" t="n">
         <v>3266.701064705836</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K72" t="n">
-        <v>0.12</v>
+        <v>-4.56</v>
       </c>
       <c r="L72" t="n">
-        <v>2.44</v>
+        <v>5.23</v>
       </c>
       <c r="M72" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="N72" t="n">
-        <v>1.59</v>
+        <v>4.68</v>
       </c>
       <c r="O72" t="n">
         <v>1.94</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45785</v>
+        <v>45786</v>
       </c>
       <c r="H73" t="n">
-        <v>3323.9</v>
+        <v>3443.9</v>
       </c>
       <c r="I73" t="n">
         <v>3341.547496051851</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.96</v>
+        <v>-5.64</v>
       </c>
       <c r="L73" t="n">
-        <v>4.41</v>
+        <v>6.65</v>
       </c>
       <c r="M73" t="n">
         <v>2.06</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="H74" t="n">
-        <v>3540.6</v>
+        <v>3495.9</v>
       </c>
       <c r="I74" t="n">
         <v>3508.349201579334</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K74" t="n">
-        <v>2.81</v>
+        <v>1.51</v>
       </c>
       <c r="L74" t="n">
         <v>3.28</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>5.15</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45867</v>
+        <v>45868</v>
       </c>
       <c r="H75" t="n">
-        <v>3495.6</v>
+        <v>3665.1</v>
       </c>
       <c r="I75" t="n">
         <v>3564.347977753695</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01</v>
+        <v>-4.84</v>
       </c>
       <c r="L75" t="n">
-        <v>1.51</v>
+        <v>5.42</v>
       </c>
       <c r="M75" t="n">
-        <v>0.66</v>
+        <v>3.62</v>
       </c>
       <c r="N75" t="n">
-        <v>2.14</v>
+        <v>4.85</v>
       </c>
       <c r="O75" t="n">
         <v>-1.26</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>6.09</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="H76" t="n">
-        <v>4019</v>
+        <v>3887.4</v>
       </c>
       <c r="I76" t="n">
         <v>4012.422489007356</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K76" t="n">
-        <v>9.66</v>
+        <v>6.07</v>
       </c>
       <c r="L76" t="n">
         <v>4.06</v>
@@ -4773,7 +5684,7 @@
         <v>1.09</v>
       </c>
       <c r="N76" t="n">
-        <v>3.09</v>
+        <v>3.27</v>
       </c>
       <c r="O76" t="n">
         <v>4.85</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>7</v>
+      </c>
+      <c r="U76" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -4809,25 +5732,25 @@
         <v>7.52</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H77" t="n">
-        <v>3921.3</v>
+        <v>4038.8</v>
       </c>
       <c r="I77" t="n">
         <v>3989.762767037024</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.87</v>
+        <v>-3.89</v>
       </c>
       <c r="L77" t="n">
-        <v>4</v>
+        <v>6.03</v>
       </c>
       <c r="M77" t="n">
-        <v>1.74</v>
+        <v>4.99</v>
       </c>
       <c r="N77" t="n">
         <v>3.66</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>7.47</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H78" t="n">
-        <v>4278.3</v>
+        <v>4066.7</v>
       </c>
       <c r="I78" t="n">
         <v>4157.426804721777</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K78" t="n">
-        <v>5.93</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>0.54</v>
+        <v>1.57</v>
       </c>
       <c r="M78" t="n">
-        <v>0.31</v>
+        <v>5.08</v>
       </c>
       <c r="N78" t="n">
-        <v>3.6</v>
+        <v>4.95</v>
       </c>
       <c r="O78" t="n">
         <v>3</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>7.79</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H79" t="n">
-        <v>3723.3</v>
+        <v>4005.9</v>
       </c>
       <c r="I79" t="n">
         <v>3761.47329234151</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K79" t="n">
-        <v>8.44</v>
+        <v>1.5</v>
       </c>
       <c r="L79" t="n">
         <v>1.84</v>
       </c>
       <c r="M79" t="n">
-        <v>4.31</v>
+        <v>6.03</v>
       </c>
       <c r="N79" t="n">
-        <v>5.22</v>
+        <v>7.59</v>
       </c>
       <c r="O79" t="n">
         <v>-4.95</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>12.06</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H80" t="n">
-        <v>4041</v>
+        <v>3991.9</v>
       </c>
       <c r="I80" t="n">
         <v>3999.42585085682</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K80" t="n">
-        <v>0.88</v>
+        <v>-0.35</v>
       </c>
       <c r="L80" t="n">
         <v>4.75</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>6.05</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="H81" t="n">
-        <v>3938.9</v>
+        <v>4025</v>
       </c>
       <c r="I81" t="n">
         <v>3960.023085571326</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K81" t="n">
-        <v>1.33</v>
+        <v>-0.83</v>
       </c>
       <c r="L81" t="n">
         <v>1.36</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,22 +6077,22 @@
         <v>6.01</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="H82" t="n">
-        <v>3946.1</v>
+        <v>3922.6</v>
       </c>
       <c r="I82" t="n">
         <v>3940.993040621311</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K82" t="n">
-        <v>-1.96</v>
+        <v>-2.54</v>
       </c>
       <c r="L82" t="n">
-        <v>1.96</v>
+        <v>2.54</v>
       </c>
       <c r="M82" t="n">
         <v>0.53</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5175,6 +6170,14 @@
       <c r="Q83" t="n">
         <v>33</v>
       </c>
+      <c r="R83" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10133,7 +11136,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="6">
@@ -10143,7 +11146,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -10153,7 +11156,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
@@ -10163,7 +11166,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10173,7 +11176,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -10183,7 +11186,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -10193,7 +11196,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -10203,7 +11206,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -10213,7 +11216,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.5</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="14">
@@ -10223,7 +11226,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.48</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -10233,7 +11236,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.45</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="16">
@@ -10243,7 +11246,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.46</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="17">
@@ -10253,7 +11256,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56.73</v>
+        <v>55.69</v>
       </c>
     </row>
     <row r="18">
@@ -10263,7 +11266,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="19">
@@ -10273,7 +11276,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="20">
@@ -10283,7 +11286,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.67</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="21">
@@ -10303,7 +11306,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -10313,7 +11316,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -10323,7 +11326,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="25">
@@ -10333,7 +11336,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="26">
@@ -10343,7 +11346,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.97</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="27">
@@ -10353,7 +11356,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.44</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="28">
@@ -10363,7 +11366,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
